--- a/InputData/land/CApULAbIFM/na-CO2 Abated per Unit Land Area by Impr For Mgmt.xlsx
+++ b/InputData/land/CApULAbIFM/na-CO2 Abated per Unit Land Area by Impr For Mgmt.xlsx
@@ -1,22 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\CApULAbIFM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215731E3-406A-4E25-BD44-958B38DCC3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="315" windowWidth="18825" windowHeight="6555"/>
+    <workbookView xWindow="4755" yWindow="2235" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Calculations" sheetId="4" r:id="rId2"/>
-    <sheet name="CApULAbIFM" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="About" sheetId="1" r:id="rId2"/>
+    <sheet name="Calculations" sheetId="4" r:id="rId3"/>
+    <sheet name="CApULAbIFM" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="acres_per_hectare">#REF!</definedName>
+    <definedName name="acres_per_million_hectares">#REF!</definedName>
+    <definedName name="C_to_CO2">'[2]Conversion Factors'!$A$4</definedName>
+    <definedName name="grams_per_ton">#REF!</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>CApULAbIFM CO2 Abated per Unit Land Area by Improved Forest Management</t>
   </si>
@@ -61,17 +91,369 @@
   </si>
   <si>
     <t>Page 2-3, Table 2-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年份</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Year</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>造林总面积</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Total Area of Afforestation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人工造林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Manual Planting</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞播造林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Airplane Planting</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>封山育林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Closed Hillsides for Afforestation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退化林修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Restoration of Degraded Forest</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人工更新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Artificial Regeneration</t>
+    </r>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>趋势值 (万吨碳/年²)</t>
+  </si>
+  <si>
+    <t>贡献占比 (相对于 NEPD​)</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>森林抚育投入 (FTI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主导地位 (最大驱动力) </t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>封山育林 (MFR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">重要补充 </t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>造林 (Afforestation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">增速较慢 (受土地限制) </t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>万吨碳/年平方</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>森林抚育 (FTI):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+553万吨/年2</t>
+    </r>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>gCO2/acre/year</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>封山育林 (MFR):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+270万吨/年2</t>
+    </r>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <r>
+      <t>造林 (Afforestation):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+160万吨/年2</t>
+    </r>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Enhanced forest management rather than afforestation has dominated China’s carbon sink over recent decades</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s43247-025-03176-2</t>
+  </si>
+  <si>
+    <r>
+      <t>Zhang, M., He, H., Brandt, M. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>et al.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s43247-025-03176-2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -79,7 +461,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -87,20 +469,94 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -108,12 +564,123 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -124,10 +691,81 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{C31B4250-04D2-4FA7-9990-8D6A3FEC8DB9}"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -135,14 +773,105 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Aforestation by province"/>
+      <sheetName val="2020-2023national total"/>
+      <sheetName val="set asides_2014to2018"/>
+      <sheetName val="Calculation"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Yearbook Stats"/>
+      <sheetName val="PLANAbPiaSY"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Conversion Factors"/>
+      <sheetName val="About"/>
+      <sheetName val="CO2 Aff &amp; Ref"/>
+      <sheetName val="VFC-PIIiCRfAaREY"/>
+      <sheetName val="Lost Value Aff &amp; Ref"/>
+      <sheetName val="VFC-LVpIIiCAbAaR"/>
+      <sheetName val="One Time Cost Aff &amp; Ref"/>
+      <sheetName val="VFC-OTCpIIiCAbAaR"/>
+      <sheetName val="Ongoing Cost Aff &amp; Ref"/>
+      <sheetName val="VFC-OCpMCAbAaR"/>
+      <sheetName val="CO2 Set Asides"/>
+      <sheetName val="VFC-PACRfFSA"/>
+      <sheetName val="Lost Value Set Asides"/>
+      <sheetName val="VFC-LVpMCAbFSA"/>
+      <sheetName val="CO2 Avoided Deforestation"/>
+      <sheetName val="VFC-PACRfAD"/>
+      <sheetName val="Lost Value Avoided Deforestatio"/>
+      <sheetName val="VFC-LVpMCAbAD"/>
+      <sheetName val="County Data"/>
+      <sheetName val="Forest Mgmt Costs"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="A4">
+            <v>3.6666666666666665</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -180,7 +909,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -252,7 +981,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,16 +1154,608 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130655D3-6B71-4957-A8FA-B4ABCA4B01DB}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="8" width="9" style="11"/>
+    <col min="9" max="9" width="33.875" style="20" customWidth="1"/>
+    <col min="10" max="11" width="33.875" style="11" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="11"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="90.75" thickBot="1">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15">
+      <c r="A2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="14">
+        <v>510.5</v>
+      </c>
+      <c r="C2" s="15">
+        <v>434.5</v>
+      </c>
+      <c r="D2" s="15">
+        <v>76</v>
+      </c>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="I2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="16">
+        <v>553</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15">
+      <c r="A3" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="18">
+        <v>495.3</v>
+      </c>
+      <c r="C3" s="19">
+        <v>397.7</v>
+      </c>
+      <c r="D3" s="19">
+        <v>97.6</v>
+      </c>
+      <c r="E3" s="19">
+        <v>121.77</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="I3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="16">
+        <v>270</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15">
+      <c r="A4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="18">
+        <v>777.1</v>
+      </c>
+      <c r="C4" s="19">
+        <v>689.6</v>
+      </c>
+      <c r="D4" s="19">
+        <v>87.5</v>
+      </c>
+      <c r="E4" s="19">
+        <v>61.3</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="I4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="16">
+        <v>160</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15">
+      <c r="A5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="18">
+        <v>911.9</v>
+      </c>
+      <c r="C5" s="19">
+        <v>843.2</v>
+      </c>
+      <c r="D5" s="19">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="E5" s="19">
+        <v>179.5</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:11" ht="15">
+      <c r="A6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="18">
+        <v>679.5</v>
+      </c>
+      <c r="C6" s="19">
+        <v>501.9</v>
+      </c>
+      <c r="D6" s="19">
+        <v>57.9</v>
+      </c>
+      <c r="E6" s="19">
+        <v>119.7</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:11" ht="15">
+      <c r="A7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="18">
+        <v>540.4</v>
+      </c>
+      <c r="C7" s="19">
+        <v>323.2</v>
+      </c>
+      <c r="D7" s="19">
+        <v>41.6</v>
+      </c>
+      <c r="E7" s="19">
+        <v>175.6</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" ht="15">
+      <c r="A8" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="18">
+        <v>383.9</v>
+      </c>
+      <c r="C8" s="19">
+        <v>244.6</v>
+      </c>
+      <c r="D8" s="19">
+        <v>27.2</v>
+      </c>
+      <c r="E8" s="19">
+        <v>112.1</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="I8" s="21">
+        <f>270/AVERAGE(E3:E22)</f>
+        <v>1.7031100682190197</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15">
+      <c r="A9" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="18">
+        <v>390.8</v>
+      </c>
+      <c r="C9" s="19">
+        <v>273.89999999999998</v>
+      </c>
+      <c r="D9" s="19">
+        <v>11.9</v>
+      </c>
+      <c r="E9" s="19">
+        <v>105.1</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="I9" s="20">
+        <f>I8/150000*10^10*3.67</f>
+        <v>416694.26335758681</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15">
+      <c r="A10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="18">
+        <v>535.4</v>
+      </c>
+      <c r="C10" s="19">
+        <v>368.5</v>
+      </c>
+      <c r="D10" s="19">
+        <v>15.4</v>
+      </c>
+      <c r="E10" s="19">
+        <v>151.5</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="K10" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15">
+      <c r="A11" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="18">
+        <v>626.20000000000005</v>
+      </c>
+      <c r="C11" s="19">
+        <v>415.6</v>
+      </c>
+      <c r="D11" s="19">
+        <v>22.6</v>
+      </c>
+      <c r="E11" s="19">
+        <v>188</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:11" ht="15">
+      <c r="A12" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="18">
+        <v>591</v>
+      </c>
+      <c r="C12" s="19">
+        <v>387.3</v>
+      </c>
+      <c r="D12" s="19">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E12" s="19">
+        <v>184.1</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:11" ht="15">
+      <c r="A13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="18">
+        <v>599.70000000000005</v>
+      </c>
+      <c r="C13" s="19">
+        <v>406.6</v>
+      </c>
+      <c r="D13" s="19">
+        <v>19.7</v>
+      </c>
+      <c r="E13" s="19">
+        <v>173.4</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:11" ht="15">
+      <c r="A14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="18">
+        <v>559.6</v>
+      </c>
+      <c r="C14" s="19">
+        <v>382.1</v>
+      </c>
+      <c r="D14" s="19">
+        <v>13.6</v>
+      </c>
+      <c r="E14" s="19">
+        <v>163.9</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+    </row>
+    <row r="15" spans="1:11" ht="15">
+      <c r="A15" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="18">
+        <v>610</v>
+      </c>
+      <c r="C15" s="19">
+        <v>421</v>
+      </c>
+      <c r="D15" s="19">
+        <v>15.4</v>
+      </c>
+      <c r="E15" s="19">
+        <v>173.6</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" spans="1:11" ht="15">
+      <c r="A16" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="18">
+        <v>555</v>
+      </c>
+      <c r="C16" s="19">
+        <v>405.3</v>
+      </c>
+      <c r="D16" s="19">
+        <v>10.8</v>
+      </c>
+      <c r="E16" s="19">
+        <v>138.9</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="A17" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="18">
+        <v>768.4</v>
+      </c>
+      <c r="C17" s="19">
+        <v>436.3</v>
+      </c>
+      <c r="D17" s="19">
+        <v>12.8</v>
+      </c>
+      <c r="E17" s="19">
+        <v>215.3</v>
+      </c>
+      <c r="F17" s="19">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="G17" s="19">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15">
+      <c r="A18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="18">
+        <v>720.4</v>
+      </c>
+      <c r="C18" s="19">
+        <v>382.4</v>
+      </c>
+      <c r="D18" s="19">
+        <v>16.2</v>
+      </c>
+      <c r="E18" s="19">
+        <v>195.4</v>
+      </c>
+      <c r="F18" s="19">
+        <v>99.1</v>
+      </c>
+      <c r="G18" s="19">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="A19" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="18">
+        <v>768.1</v>
+      </c>
+      <c r="C19" s="19">
+        <v>429.6</v>
+      </c>
+      <c r="D19" s="19">
+        <v>14.1</v>
+      </c>
+      <c r="E19" s="19">
+        <v>165.7</v>
+      </c>
+      <c r="F19" s="19">
+        <v>128.1</v>
+      </c>
+      <c r="G19" s="19">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
+      <c r="A20" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="18">
+        <v>729.9</v>
+      </c>
+      <c r="C20" s="19">
+        <v>367.8</v>
+      </c>
+      <c r="D20" s="19">
+        <v>13.5</v>
+      </c>
+      <c r="E20" s="19">
+        <v>178.5</v>
+      </c>
+      <c r="F20" s="19">
+        <v>132.9</v>
+      </c>
+      <c r="G20" s="19">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15">
+      <c r="A21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="18">
+        <v>739</v>
+      </c>
+      <c r="C21" s="19">
+        <v>345.8</v>
+      </c>
+      <c r="D21" s="19">
+        <v>12.6</v>
+      </c>
+      <c r="E21" s="19">
+        <v>189.8</v>
+      </c>
+      <c r="F21" s="19">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="G21" s="19">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
+      <c r="A22" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="18">
+        <v>693.4</v>
+      </c>
+      <c r="C22" s="19">
+        <v>300</v>
+      </c>
+      <c r="D22" s="19">
+        <v>15.1</v>
+      </c>
+      <c r="E22" s="19">
+        <v>177.5</v>
+      </c>
+      <c r="F22" s="19">
+        <v>162</v>
+      </c>
+      <c r="G22" s="19">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
+      <c r="A23" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="18">
+        <v>375.4</v>
+      </c>
+      <c r="C23" s="19">
+        <v>108.5</v>
+      </c>
+      <c r="D23" s="19">
+        <v>17.2</v>
+      </c>
+      <c r="E23" s="19">
+        <v>123.5</v>
+      </c>
+      <c r="F23" s="19">
+        <v>101.1</v>
+      </c>
+      <c r="G23" s="19">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
+      <c r="A24" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="18">
+        <v>420.3</v>
+      </c>
+      <c r="C24" s="19">
+        <v>93.1</v>
+      </c>
+      <c r="D24" s="19">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E24" s="19">
+        <v>105.7</v>
+      </c>
+      <c r="F24" s="19">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="G24" s="19">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A25" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="24">
+        <v>463.6</v>
+      </c>
+      <c r="C25" s="25">
+        <v>101.4</v>
+      </c>
+      <c r="D25" s="25">
+        <v>6.7</v>
+      </c>
+      <c r="E25" s="25">
+        <v>113.3</v>
+      </c>
+      <c r="F25" s="25">
+        <v>179.6</v>
+      </c>
+      <c r="G25" s="25">
+        <v>62.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="108.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -442,56 +1763,79 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="4">
         <v>2005</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:2" s="28" customFormat="1">
+      <c r="A9" s="26"/>
+      <c r="B9" s="29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="28" customFormat="1">
+      <c r="B10" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="28" customFormat="1">
+      <c r="B11" s="27">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="28" customFormat="1">
+      <c r="B12" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>2.1</v>
       </c>
@@ -502,7 +1846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>3.1</v>
       </c>
@@ -513,7 +1857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <f>AVERAGE(A2:A3)</f>
         <v>2.6</v>
@@ -525,7 +1869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="3">
         <f>A4*10^6</f>
         <v>2600000</v>
@@ -538,36 +1882,39 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3">
-        <f>Calculations!A6</f>
-        <v>2600000</v>
+      <c r="B2" s="6">
+        <f>Sheet1!I9</f>
+        <v>416694.26335758681</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>